--- a/Modules/KickAid/KickAid_BOM.xlsx
+++ b/Modules/KickAid/KickAid_BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\My-Dev\Modular Synth\Avalon Harmonics\KickAid\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D52E714-8F2E-4469-93F1-DFB2F4AF2672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46C02DCD-A8B6-48E6-A522-9045E7E178D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
@@ -146,15 +146,9 @@
     <t>Pushernut</t>
   </si>
   <si>
-    <t>https://pushermanproductions.com/product/black-smooth-edge-jack-nuts-pack-of-25/</t>
-  </si>
-  <si>
     <t>Gold</t>
   </si>
   <si>
-    <t>https://pushermanproductions.com/product/pushernuts-gold-smooth-edge-jack-nuts-pack-of-25/</t>
-  </si>
-  <si>
     <t>Potentiometer Knob</t>
   </si>
   <si>
@@ -633,9 +627,6 @@
     <t>https://www.tme.eu/de/en/details/zl201-40g/pin-headers/connfly/ds1021-1-40sf11-b/</t>
   </si>
   <si>
-    <t>https://www.tme.eu/de/en/details/zl202-80g/pin-headers/connfly/ds1021-2-40sf11/</t>
-  </si>
-  <si>
     <t>Parts  with underline are on the front PCB!</t>
   </si>
   <si>
@@ -1368,6 +1359,15 @@
   </si>
   <si>
     <t>https://www.buerklin.com/en/p/vishay/wirewound-resistors/mba02040c2403fct00/14E750/</t>
+  </si>
+  <si>
+    <t>https://pushermanproductions.com/products/pushernuts-round-mini-jack-nuts-pack-of-25?variant=57164621578504</t>
+  </si>
+  <si>
+    <t>https://pushermanproductions.com/products/pushernuts-round-mini-jack-nuts-pack-of-25?variant=57166910816520</t>
+  </si>
+  <si>
+    <t>https://www.tme.eu/de/en/details/zl202-10g/pin-headers/connfly/ds1021-2-5sf11-b/</t>
   </si>
 </sst>
 </file>
@@ -2363,7 +2363,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="G2" s="1"/>
       <c r="J2" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -2398,16 +2398,16 @@
         <v>100</v>
       </c>
       <c r="C3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E3" t="s">
         <v>16</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>27</v>
@@ -2421,16 +2421,16 @@
         <v>220</v>
       </c>
       <c r="C4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>27</v>
@@ -2444,16 +2444,16 @@
         <v>330</v>
       </c>
       <c r="C5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E5" t="s">
         <v>16</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>27</v>
@@ -2467,16 +2467,16 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E6" t="s">
         <v>16</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>27</v>
@@ -2487,19 +2487,19 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E7" t="s">
         <v>16</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>27</v>
@@ -2510,19 +2510,19 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C8" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D8" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E8" t="s">
         <v>16</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>27</v>
@@ -2533,22 +2533,22 @@
         <v>2</v>
       </c>
       <c r="B9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C9" t="s">
+        <v>133</v>
+      </c>
+      <c r="D9" t="s">
         <v>78</v>
-      </c>
-      <c r="C9" t="s">
-        <v>135</v>
-      </c>
-      <c r="D9" t="s">
-        <v>80</v>
       </c>
       <c r="E9" t="s">
         <v>16</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J9" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -2556,13 +2556,13 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D10" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E10" t="s">
         <v>16</v>
@@ -2571,7 +2571,7 @@
         <v>27</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -2579,22 +2579,22 @@
         <v>2</v>
       </c>
       <c r="B11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C11" t="s">
+        <v>133</v>
+      </c>
+      <c r="D11" t="s">
         <v>79</v>
-      </c>
-      <c r="C11" t="s">
-        <v>135</v>
-      </c>
-      <c r="D11" t="s">
-        <v>81</v>
       </c>
       <c r="E11" t="s">
         <v>16</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J11" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -2602,19 +2602,19 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C12" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E12" t="s">
         <v>16</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>27</v>
@@ -2625,19 +2625,19 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D13" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E13" t="s">
         <v>16</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>27</v>
@@ -2651,16 +2651,16 @@
         <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D14" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E14" t="s">
         <v>16</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>27</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C15" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D15" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E15" t="s">
         <v>16</v>
@@ -2686,7 +2686,7 @@
         <v>27</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -2694,13 +2694,13 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D16" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E16" t="s">
         <v>16</v>
@@ -2709,7 +2709,7 @@
         <v>27</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -2717,19 +2717,19 @@
         <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C17" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D17" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E17" t="s">
         <v>16</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>27</v>
@@ -2743,19 +2743,19 @@
         <v>12</v>
       </c>
       <c r="C18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D18" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="D18" s="9" t="s">
-        <v>65</v>
-      </c>
       <c r="E18" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -2763,22 +2763,22 @@
         <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C19" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D19" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E19" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -2789,19 +2789,19 @@
         <v>11</v>
       </c>
       <c r="C20" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D20" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E20" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -2809,22 +2809,22 @@
         <v>2</v>
       </c>
       <c r="B21" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C21" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D21" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E21" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="J21" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -2835,19 +2835,19 @@
         <v>7</v>
       </c>
       <c r="C22" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D22" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E22" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="J22" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -2855,22 +2855,22 @@
         <v>3</v>
       </c>
       <c r="B23" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D23" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E23" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="J23" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -2881,19 +2881,19 @@
         <v>5</v>
       </c>
       <c r="C24" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D24" t="s">
         <v>6</v>
       </c>
       <c r="E24" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="J24" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -2913,10 +2913,10 @@
         <v>24</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J25" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -2930,16 +2930,16 @@
         <v>18</v>
       </c>
       <c r="D26" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E26" t="s">
         <v>25</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J26" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -2947,22 +2947,22 @@
         <v>1</v>
       </c>
       <c r="B27" t="s">
+        <v>82</v>
+      </c>
+      <c r="C27" t="s">
+        <v>83</v>
+      </c>
+      <c r="D27" t="s">
+        <v>85</v>
+      </c>
+      <c r="E27" t="s">
         <v>84</v>
       </c>
-      <c r="C27" t="s">
-        <v>85</v>
-      </c>
-      <c r="D27" t="s">
-        <v>87</v>
-      </c>
-      <c r="E27" t="s">
-        <v>86</v>
-      </c>
       <c r="F27" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J27" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -2973,16 +2973,16 @@
         <v>23</v>
       </c>
       <c r="C28" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E28" t="s">
         <v>23</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="J28" s="3" t="s">
         <v>28</v>
@@ -2999,13 +2999,13 @@
         <v>22</v>
       </c>
       <c r="D29" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E29" t="s">
         <v>23</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>28</v>
@@ -3022,16 +3022,16 @@
         <v>19</v>
       </c>
       <c r="D30" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E30" t="s">
         <v>20</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="J30" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -3039,22 +3039,22 @@
         <v>1</v>
       </c>
       <c r="B31" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C31" t="s">
         <v>19</v>
       </c>
       <c r="D31" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E31" t="s">
         <v>20</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="J31" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -3062,22 +3062,22 @@
         <v>1</v>
       </c>
       <c r="B32" t="s">
+        <v>90</v>
+      </c>
+      <c r="C32" t="s">
+        <v>91</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="E32" t="s">
         <v>92</v>
       </c>
-      <c r="C32" t="s">
-        <v>93</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="E32" t="s">
-        <v>94</v>
-      </c>
       <c r="F32" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="J32" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -3085,22 +3085,22 @@
         <v>1</v>
       </c>
       <c r="B33" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C33" t="s">
         <v>19</v>
       </c>
       <c r="D33" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E33" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J33" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -3108,22 +3108,22 @@
         <v>1</v>
       </c>
       <c r="B34" t="s">
+        <v>97</v>
+      </c>
+      <c r="C34" t="s">
+        <v>98</v>
+      </c>
+      <c r="D34" t="s">
+        <v>100</v>
+      </c>
+      <c r="E34" t="s">
         <v>99</v>
       </c>
-      <c r="C34" t="s">
-        <v>100</v>
-      </c>
-      <c r="D34" t="s">
-        <v>102</v>
-      </c>
-      <c r="E34" t="s">
-        <v>101</v>
-      </c>
       <c r="F34" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="J34" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -3131,22 +3131,22 @@
         <v>1</v>
       </c>
       <c r="B35" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C35" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E35" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>29</v>
       </c>
       <c r="J35" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -3154,22 +3154,22 @@
         <v>3</v>
       </c>
       <c r="B36" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C36" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D36" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E36" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>29</v>
       </c>
       <c r="J36" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -3177,22 +3177,22 @@
         <v>1</v>
       </c>
       <c r="B37" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C37" t="s">
+        <v>104</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="E37" t="s">
+        <v>105</v>
+      </c>
+      <c r="F37" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="D37" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="E37" t="s">
-        <v>107</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>108</v>
-      </c>
       <c r="J37" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -3200,19 +3200,19 @@
         <v>1</v>
       </c>
       <c r="B38" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C38" t="s">
+        <v>104</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="E38" t="s">
+        <v>105</v>
+      </c>
+      <c r="F38" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="E38" t="s">
-        <v>107</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -3220,19 +3220,19 @@
         <v>2</v>
       </c>
       <c r="B39" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C39" t="s">
+        <v>104</v>
+      </c>
+      <c r="D39" t="s">
+        <v>177</v>
+      </c>
+      <c r="E39" t="s">
+        <v>105</v>
+      </c>
+      <c r="F39" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="D39" t="s">
-        <v>180</v>
-      </c>
-      <c r="E39" t="s">
-        <v>107</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -3240,19 +3240,19 @@
         <v>1</v>
       </c>
       <c r="B40" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C40" t="s">
+        <v>104</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E40" t="s">
+        <v>105</v>
+      </c>
+      <c r="F40" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="E40" t="s">
-        <v>107</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -3260,19 +3260,19 @@
         <v>1</v>
       </c>
       <c r="B41" t="s">
+        <v>103</v>
+      </c>
+      <c r="C41" t="s">
+        <v>104</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="E41" t="s">
         <v>105</v>
       </c>
-      <c r="C41" t="s">
+      <c r="F41" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="E41" t="s">
-        <v>107</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -3280,22 +3280,22 @@
         <v>4</v>
       </c>
       <c r="B42" t="s">
+        <v>117</v>
+      </c>
+      <c r="C42" t="s">
+        <v>118</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="E42" t="s">
         <v>119</v>
       </c>
-      <c r="C42" t="s">
-        <v>120</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="E42" t="s">
-        <v>121</v>
-      </c>
       <c r="F42" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="J42" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -3303,22 +3303,22 @@
         <v>1</v>
       </c>
       <c r="B43" t="s">
+        <v>66</v>
+      </c>
+      <c r="C43" t="s">
+        <v>124</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="E43" t="s">
+        <v>67</v>
+      </c>
+      <c r="F43" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C43" t="s">
-        <v>126</v>
-      </c>
-      <c r="D43" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="E43" t="s">
-        <v>69</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="J43" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -3326,13 +3326,13 @@
         <v>8</v>
       </c>
       <c r="B44" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C44" t="s">
         <v>30</v>
       </c>
       <c r="D44" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E44" t="s">
         <v>21</v>
@@ -3341,7 +3341,7 @@
         <v>31</v>
       </c>
       <c r="J44" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
@@ -3349,22 +3349,22 @@
         <v>3</v>
       </c>
       <c r="B45" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C45" t="s">
         <v>32</v>
       </c>
       <c r="D45" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E45" t="s">
         <v>15</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="J45" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -3372,22 +3372,22 @@
         <v>4</v>
       </c>
       <c r="B46" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C46" t="s">
         <v>32</v>
       </c>
       <c r="D46" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E46" t="s">
         <v>15</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="J46" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
@@ -3395,22 +3395,22 @@
         <v>3</v>
       </c>
       <c r="B47" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C47" t="s">
         <v>33</v>
       </c>
       <c r="D47" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E47" t="s">
         <v>15</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -3418,22 +3418,22 @@
         <v>4</v>
       </c>
       <c r="B48" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C48" t="s">
         <v>33</v>
       </c>
       <c r="D48" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E48" t="s">
         <v>15</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
@@ -3453,10 +3453,10 @@
         <v>15</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>171</v>
+        <v>205</v>
       </c>
       <c r="J49" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
@@ -3464,19 +3464,19 @@
         <v>3</v>
       </c>
       <c r="B51" t="s">
+        <v>43</v>
+      </c>
+      <c r="C51" t="s">
+        <v>44</v>
+      </c>
+      <c r="E51" t="s">
         <v>45</v>
       </c>
-      <c r="C51" t="s">
+      <c r="F51" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E51" t="s">
-        <v>47</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="J51" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
@@ -3484,19 +3484,19 @@
         <v>3</v>
       </c>
       <c r="B52" t="s">
+        <v>48</v>
+      </c>
+      <c r="C52" t="s">
+        <v>49</v>
+      </c>
+      <c r="E52" t="s">
         <v>50</v>
       </c>
-      <c r="C52" t="s">
-        <v>51</v>
-      </c>
-      <c r="E52" t="s">
-        <v>52</v>
-      </c>
       <c r="F52" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J52" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
@@ -3504,19 +3504,19 @@
         <v>3</v>
       </c>
       <c r="B53" t="s">
+        <v>51</v>
+      </c>
+      <c r="C53" t="s">
+        <v>54</v>
+      </c>
+      <c r="E53" t="s">
         <v>53</v>
       </c>
-      <c r="C53" t="s">
-        <v>56</v>
-      </c>
-      <c r="E53" t="s">
-        <v>55</v>
-      </c>
       <c r="F53" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J53" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
@@ -3530,13 +3530,13 @@
         <v>36</v>
       </c>
       <c r="E55" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>37</v>
+        <v>203</v>
       </c>
       <c r="J55" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -3544,19 +3544,19 @@
         <v>5</v>
       </c>
       <c r="B56" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C56" t="s">
         <v>36</v>
       </c>
       <c r="E56" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>39</v>
+        <v>204</v>
       </c>
       <c r="J56" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
@@ -3567,16 +3567,16 @@
         <v>35</v>
       </c>
       <c r="C57" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E57" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="J57" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
@@ -3584,19 +3584,19 @@
         <v>4</v>
       </c>
       <c r="B58" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C58" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E58" t="s">
+        <v>38</v>
+      </c>
+      <c r="F58" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="J58" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
@@ -3607,21 +3607,21 @@
         <v>35</v>
       </c>
       <c r="C59" t="s">
+        <v>126</v>
+      </c>
+      <c r="E59" t="s">
+        <v>127</v>
+      </c>
+      <c r="F59" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="E59" t="s">
-        <v>129</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>130</v>
-      </c>
       <c r="J59" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B61" s="9" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
@@ -3629,22 +3629,22 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B63" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B64" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="65" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B65" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="66" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B66" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -3660,70 +3660,70 @@
     <hyperlink ref="F51" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
     <hyperlink ref="F52" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
     <hyperlink ref="F53" r:id="rId11" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="F55" r:id="rId12" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="F56" r:id="rId13" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="J47" r:id="rId14" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="F45" r:id="rId15" xr:uid="{8471C66D-2803-4E39-A4C9-56382FB4FA7C}"/>
-    <hyperlink ref="F49" r:id="rId16" xr:uid="{6ABC6086-4872-4A5E-A074-AF133E043F03}"/>
-    <hyperlink ref="F19" r:id="rId17" xr:uid="{0078F1D0-2252-4276-B4FA-F7758611CB55}"/>
-    <hyperlink ref="F20" r:id="rId18" xr:uid="{C63AEC0D-8CBC-4750-A708-A0BDA2E3A104}"/>
-    <hyperlink ref="J20" r:id="rId19" xr:uid="{8C810300-BA98-4ED0-8B65-62815602E020}"/>
-    <hyperlink ref="J19" r:id="rId20" xr:uid="{D56F3FC4-21F0-446F-A842-9A94AA04813F}"/>
-    <hyperlink ref="F21" r:id="rId21" xr:uid="{1D4215ED-E169-427E-90FC-04FAE5A9B71D}"/>
-    <hyperlink ref="F46" r:id="rId22" xr:uid="{70623DF7-AD80-49BE-8BCF-99E43397C3C6}"/>
-    <hyperlink ref="J48" r:id="rId23" xr:uid="{10E960AF-C6C6-47C3-9E72-05533B5ED5AD}"/>
-    <hyperlink ref="F43" r:id="rId24" xr:uid="{362C4AFE-495E-47D3-8980-A94395D8849C}"/>
-    <hyperlink ref="J6" r:id="rId25" xr:uid="{9E0ED9E0-C3A3-4348-BB6F-5C429B9E61E7}"/>
-    <hyperlink ref="J14" r:id="rId26" xr:uid="{AC848EF4-7FAB-4E48-AF09-F798B5BC950A}"/>
-    <hyperlink ref="J8" r:id="rId27" xr:uid="{238CA172-A99C-46CD-9FBB-BE7CBE8D9023}"/>
-    <hyperlink ref="J12" r:id="rId28" xr:uid="{7C381042-415D-491B-ACA4-70B1B604E6FF}"/>
-    <hyperlink ref="J3" r:id="rId29" xr:uid="{ED0023B2-A5EC-4035-85B5-DE2DDC612B77}"/>
-    <hyperlink ref="J4" r:id="rId30" xr:uid="{7EEEE007-B054-4096-B66B-765D5AD446BD}"/>
-    <hyperlink ref="J5" r:id="rId31" xr:uid="{6C1ADA1E-CB09-4E33-8184-EF1E1E303B88}"/>
-    <hyperlink ref="J7" r:id="rId32" xr:uid="{58A8E3CE-CD3F-43A3-B946-EE7AAC959BB8}"/>
-    <hyperlink ref="F10" r:id="rId33" xr:uid="{B4611C36-E3CD-48A1-B558-378FFEE572B7}"/>
-    <hyperlink ref="J13" r:id="rId34" xr:uid="{40377A08-FCE6-4F89-9187-96A00B93A312}"/>
-    <hyperlink ref="F16" r:id="rId35" xr:uid="{5A1179F6-3A84-498D-87AF-DBF1D5EAF071}"/>
-    <hyperlink ref="F9" r:id="rId36" xr:uid="{F2E3BA95-EDCE-4952-9E03-A8804711C4CB}"/>
-    <hyperlink ref="F11" r:id="rId37" xr:uid="{4C536C75-1E7B-4E8E-AC70-3B143F26311E}"/>
-    <hyperlink ref="F18" r:id="rId38" xr:uid="{9DE94678-EFDC-4596-B004-CE73B42552E7}"/>
-    <hyperlink ref="J18" r:id="rId39" xr:uid="{22025D74-97DB-4D2B-BB71-13FAD64FC821}"/>
-    <hyperlink ref="F27" r:id="rId40" xr:uid="{0DF77104-940B-4656-902E-D3B4A729F975}"/>
-    <hyperlink ref="F31" r:id="rId41" xr:uid="{0234E1EC-3124-4C89-975E-D13FE095B07F}"/>
-    <hyperlink ref="F32" r:id="rId42" xr:uid="{DB5928A3-0C2C-41C8-94E2-173BFEB2B0BB}"/>
-    <hyperlink ref="F33" r:id="rId43" xr:uid="{24D2838B-698C-49F3-A89F-82FDF5909F9B}"/>
-    <hyperlink ref="F34" r:id="rId44" xr:uid="{5354C7EC-6A56-490A-97A1-06170A361210}"/>
-    <hyperlink ref="J28" r:id="rId45" xr:uid="{DA65564B-FC06-44AA-BE9E-CDEC85344EA4}"/>
-    <hyperlink ref="F37" r:id="rId46" xr:uid="{9B529563-7FF1-4CBB-B28F-CF26D80CBBD0}"/>
-    <hyperlink ref="F38" r:id="rId47" xr:uid="{19B2C35A-2AC5-48E0-ADAA-8A862A2BE8D1}"/>
-    <hyperlink ref="F40" r:id="rId48" xr:uid="{95AFB553-4A2D-4412-8ADD-9C777E0114C2}"/>
-    <hyperlink ref="F41" r:id="rId49" xr:uid="{B4A17999-A824-419D-96B6-45991272181C}"/>
-    <hyperlink ref="F39" r:id="rId50" xr:uid="{748FCFF4-A3F0-42DC-A53F-B6C8D0F870A5}"/>
-    <hyperlink ref="F36" r:id="rId51" xr:uid="{8CE5E525-65D3-417D-A66F-FDAA297CA9FB}"/>
-    <hyperlink ref="F35" r:id="rId52" xr:uid="{DF66115C-265B-4566-AA35-F0AD032F438C}"/>
-    <hyperlink ref="F42" r:id="rId53" xr:uid="{932A7A9F-0EC3-41B4-8980-42A6D5FC0033}"/>
-    <hyperlink ref="F59" r:id="rId54" xr:uid="{7A52BB5F-2156-4696-A05E-A65CF92F76E9}"/>
-    <hyperlink ref="F57" r:id="rId55" xr:uid="{2CBD1E2B-EA04-41D5-947D-738E19704CE1}"/>
-    <hyperlink ref="F23" r:id="rId56" xr:uid="{D7D22B2B-3A31-4EBC-A56A-9A899E1E05E5}"/>
-    <hyperlink ref="F15" r:id="rId57" xr:uid="{67316A66-E885-4019-9B97-023E307D9CB3}"/>
-    <hyperlink ref="F3" r:id="rId58" xr:uid="{B02C8DF0-BB09-4FA6-B67E-C7A7B9EEB465}"/>
-    <hyperlink ref="F4" r:id="rId59" xr:uid="{BB0BB101-C150-49C2-8F2D-51BB0D499267}"/>
-    <hyperlink ref="F5" r:id="rId60" xr:uid="{58391DA3-3BFE-43C8-B512-BEFC33E500EA}"/>
-    <hyperlink ref="F6" r:id="rId61" xr:uid="{1A46D2A4-F531-45F8-B5FA-A9ABCEFEEF0A}"/>
-    <hyperlink ref="F7" r:id="rId62" xr:uid="{159D1D76-29F3-41BE-879A-3BB047A858DE}"/>
-    <hyperlink ref="F8" r:id="rId63" xr:uid="{679F6075-2AC2-48BA-9D9E-A7FA02A58128}"/>
-    <hyperlink ref="F12" r:id="rId64" xr:uid="{E6F9E951-725F-496F-8A3A-9F5DA1D9E614}"/>
-    <hyperlink ref="F13" r:id="rId65" xr:uid="{DB9D0360-FD3F-451A-A90D-5E3B558DF116}"/>
-    <hyperlink ref="F14" r:id="rId66" xr:uid="{2E579FF5-E003-4DED-AF14-BFC5B0D4309E}"/>
-    <hyperlink ref="F29" r:id="rId67" xr:uid="{62F7C14B-AFF7-4188-B463-597C440C8DE9}"/>
-    <hyperlink ref="F28" r:id="rId68" xr:uid="{A0AE6722-7DAF-47AF-9D23-B4599823780B}"/>
-    <hyperlink ref="F48" r:id="rId69" xr:uid="{3162AEA0-F325-498D-B7F8-4E76C8A146C1}"/>
-    <hyperlink ref="F47" r:id="rId70" xr:uid="{37C42E84-80D8-4CD9-A64C-BAD19903C9A5}"/>
-    <hyperlink ref="J10" r:id="rId71" xr:uid="{D8AF967F-D44E-42C9-8F2B-D5EB9F8AAAD4}"/>
-    <hyperlink ref="J15" r:id="rId72" xr:uid="{35FE4693-DDA3-4377-A2A9-B5A4BE55BB87}"/>
-    <hyperlink ref="J16" r:id="rId73" xr:uid="{D6346564-BC0F-4791-86F5-BE2F1D426945}"/>
-    <hyperlink ref="F17" r:id="rId74" xr:uid="{BE8BCBD6-1941-4587-8CEA-0C29F0C509F9}"/>
-    <hyperlink ref="J17" r:id="rId75" xr:uid="{3C36A0C5-6472-4EF1-9153-9339A6F47B44}"/>
+    <hyperlink ref="J47" r:id="rId12" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="F45" r:id="rId13" xr:uid="{8471C66D-2803-4E39-A4C9-56382FB4FA7C}"/>
+    <hyperlink ref="F19" r:id="rId14" xr:uid="{0078F1D0-2252-4276-B4FA-F7758611CB55}"/>
+    <hyperlink ref="F20" r:id="rId15" xr:uid="{C63AEC0D-8CBC-4750-A708-A0BDA2E3A104}"/>
+    <hyperlink ref="J20" r:id="rId16" xr:uid="{8C810300-BA98-4ED0-8B65-62815602E020}"/>
+    <hyperlink ref="J19" r:id="rId17" xr:uid="{D56F3FC4-21F0-446F-A842-9A94AA04813F}"/>
+    <hyperlink ref="F21" r:id="rId18" xr:uid="{1D4215ED-E169-427E-90FC-04FAE5A9B71D}"/>
+    <hyperlink ref="F46" r:id="rId19" xr:uid="{70623DF7-AD80-49BE-8BCF-99E43397C3C6}"/>
+    <hyperlink ref="J48" r:id="rId20" xr:uid="{10E960AF-C6C6-47C3-9E72-05533B5ED5AD}"/>
+    <hyperlink ref="F43" r:id="rId21" xr:uid="{362C4AFE-495E-47D3-8980-A94395D8849C}"/>
+    <hyperlink ref="J6" r:id="rId22" xr:uid="{9E0ED9E0-C3A3-4348-BB6F-5C429B9E61E7}"/>
+    <hyperlink ref="J14" r:id="rId23" xr:uid="{AC848EF4-7FAB-4E48-AF09-F798B5BC950A}"/>
+    <hyperlink ref="J8" r:id="rId24" xr:uid="{238CA172-A99C-46CD-9FBB-BE7CBE8D9023}"/>
+    <hyperlink ref="J12" r:id="rId25" xr:uid="{7C381042-415D-491B-ACA4-70B1B604E6FF}"/>
+    <hyperlink ref="J3" r:id="rId26" xr:uid="{ED0023B2-A5EC-4035-85B5-DE2DDC612B77}"/>
+    <hyperlink ref="J4" r:id="rId27" xr:uid="{7EEEE007-B054-4096-B66B-765D5AD446BD}"/>
+    <hyperlink ref="J5" r:id="rId28" xr:uid="{6C1ADA1E-CB09-4E33-8184-EF1E1E303B88}"/>
+    <hyperlink ref="J7" r:id="rId29" xr:uid="{58A8E3CE-CD3F-43A3-B946-EE7AAC959BB8}"/>
+    <hyperlink ref="F10" r:id="rId30" xr:uid="{B4611C36-E3CD-48A1-B558-378FFEE572B7}"/>
+    <hyperlink ref="J13" r:id="rId31" xr:uid="{40377A08-FCE6-4F89-9187-96A00B93A312}"/>
+    <hyperlink ref="F16" r:id="rId32" xr:uid="{5A1179F6-3A84-498D-87AF-DBF1D5EAF071}"/>
+    <hyperlink ref="F9" r:id="rId33" xr:uid="{F2E3BA95-EDCE-4952-9E03-A8804711C4CB}"/>
+    <hyperlink ref="F11" r:id="rId34" xr:uid="{4C536C75-1E7B-4E8E-AC70-3B143F26311E}"/>
+    <hyperlink ref="F18" r:id="rId35" xr:uid="{9DE94678-EFDC-4596-B004-CE73B42552E7}"/>
+    <hyperlink ref="J18" r:id="rId36" xr:uid="{22025D74-97DB-4D2B-BB71-13FAD64FC821}"/>
+    <hyperlink ref="F27" r:id="rId37" xr:uid="{0DF77104-940B-4656-902E-D3B4A729F975}"/>
+    <hyperlink ref="F31" r:id="rId38" xr:uid="{0234E1EC-3124-4C89-975E-D13FE095B07F}"/>
+    <hyperlink ref="F32" r:id="rId39" xr:uid="{DB5928A3-0C2C-41C8-94E2-173BFEB2B0BB}"/>
+    <hyperlink ref="F33" r:id="rId40" xr:uid="{24D2838B-698C-49F3-A89F-82FDF5909F9B}"/>
+    <hyperlink ref="F34" r:id="rId41" xr:uid="{5354C7EC-6A56-490A-97A1-06170A361210}"/>
+    <hyperlink ref="J28" r:id="rId42" xr:uid="{DA65564B-FC06-44AA-BE9E-CDEC85344EA4}"/>
+    <hyperlink ref="F37" r:id="rId43" xr:uid="{9B529563-7FF1-4CBB-B28F-CF26D80CBBD0}"/>
+    <hyperlink ref="F38" r:id="rId44" xr:uid="{19B2C35A-2AC5-48E0-ADAA-8A862A2BE8D1}"/>
+    <hyperlink ref="F40" r:id="rId45" xr:uid="{95AFB553-4A2D-4412-8ADD-9C777E0114C2}"/>
+    <hyperlink ref="F41" r:id="rId46" xr:uid="{B4A17999-A824-419D-96B6-45991272181C}"/>
+    <hyperlink ref="F39" r:id="rId47" xr:uid="{748FCFF4-A3F0-42DC-A53F-B6C8D0F870A5}"/>
+    <hyperlink ref="F36" r:id="rId48" xr:uid="{8CE5E525-65D3-417D-A66F-FDAA297CA9FB}"/>
+    <hyperlink ref="F35" r:id="rId49" xr:uid="{DF66115C-265B-4566-AA35-F0AD032F438C}"/>
+    <hyperlink ref="F42" r:id="rId50" xr:uid="{932A7A9F-0EC3-41B4-8980-42A6D5FC0033}"/>
+    <hyperlink ref="F59" r:id="rId51" xr:uid="{7A52BB5F-2156-4696-A05E-A65CF92F76E9}"/>
+    <hyperlink ref="F57" r:id="rId52" xr:uid="{2CBD1E2B-EA04-41D5-947D-738E19704CE1}"/>
+    <hyperlink ref="F23" r:id="rId53" xr:uid="{D7D22B2B-3A31-4EBC-A56A-9A899E1E05E5}"/>
+    <hyperlink ref="F15" r:id="rId54" xr:uid="{67316A66-E885-4019-9B97-023E307D9CB3}"/>
+    <hyperlink ref="F3" r:id="rId55" xr:uid="{B02C8DF0-BB09-4FA6-B67E-C7A7B9EEB465}"/>
+    <hyperlink ref="F4" r:id="rId56" xr:uid="{BB0BB101-C150-49C2-8F2D-51BB0D499267}"/>
+    <hyperlink ref="F5" r:id="rId57" xr:uid="{58391DA3-3BFE-43C8-B512-BEFC33E500EA}"/>
+    <hyperlink ref="F6" r:id="rId58" xr:uid="{1A46D2A4-F531-45F8-B5FA-A9ABCEFEEF0A}"/>
+    <hyperlink ref="F7" r:id="rId59" xr:uid="{159D1D76-29F3-41BE-879A-3BB047A858DE}"/>
+    <hyperlink ref="F8" r:id="rId60" xr:uid="{679F6075-2AC2-48BA-9D9E-A7FA02A58128}"/>
+    <hyperlink ref="F12" r:id="rId61" xr:uid="{E6F9E951-725F-496F-8A3A-9F5DA1D9E614}"/>
+    <hyperlink ref="F13" r:id="rId62" xr:uid="{DB9D0360-FD3F-451A-A90D-5E3B558DF116}"/>
+    <hyperlink ref="F14" r:id="rId63" xr:uid="{2E579FF5-E003-4DED-AF14-BFC5B0D4309E}"/>
+    <hyperlink ref="F29" r:id="rId64" xr:uid="{62F7C14B-AFF7-4188-B463-597C440C8DE9}"/>
+    <hyperlink ref="F28" r:id="rId65" xr:uid="{A0AE6722-7DAF-47AF-9D23-B4599823780B}"/>
+    <hyperlink ref="F48" r:id="rId66" xr:uid="{3162AEA0-F325-498D-B7F8-4E76C8A146C1}"/>
+    <hyperlink ref="F47" r:id="rId67" xr:uid="{37C42E84-80D8-4CD9-A64C-BAD19903C9A5}"/>
+    <hyperlink ref="J10" r:id="rId68" xr:uid="{D8AF967F-D44E-42C9-8F2B-D5EB9F8AAAD4}"/>
+    <hyperlink ref="J15" r:id="rId69" xr:uid="{35FE4693-DDA3-4377-A2A9-B5A4BE55BB87}"/>
+    <hyperlink ref="J16" r:id="rId70" xr:uid="{D6346564-BC0F-4791-86F5-BE2F1D426945}"/>
+    <hyperlink ref="F17" r:id="rId71" xr:uid="{BE8BCBD6-1941-4587-8CEA-0C29F0C509F9}"/>
+    <hyperlink ref="J17" r:id="rId72" xr:uid="{3C36A0C5-6472-4EF1-9153-9339A6F47B44}"/>
+    <hyperlink ref="F55" r:id="rId73" xr:uid="{FFB65FAE-04E3-4FA0-9868-5E6798B1C967}"/>
+    <hyperlink ref="F56" r:id="rId74" xr:uid="{CFDBF239-7FC8-4FC4-9EF8-CD7394472B6D}"/>
+    <hyperlink ref="F49" r:id="rId75" xr:uid="{71E8E4F3-6136-4203-8101-0CD684A1C254}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId76"/>
